--- a/docs/plano_e_fluxo_de_testes_TCC.xlsx
+++ b/docs/plano_e_fluxo_de_testes_TCC.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Massa de ocorrências reais cadastradas previamente no backend (via API ou diretamente no banco), cobrindo os cenários necessários para as tarefas do roteiro (ex.: ocorrências com diferentes níveis de risco, em diferentes regiões e períodos) — ver backend/benchmark/gerar_dados.py para geração de massa reprodutível quando aplicável.</t>
+          <t>Ocorrências de demonstração de São Caetano do Sul (30 registros, níveis/fontes/períodos variados) carregadas por backend/dados_demo.py e marcadas com id_usuario='demo-seed' — não são alagamentos reais. Para o benchmark, massa sintética reprodutível de backend/benchmark/gerar_dados.py.</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Não Iniciado</t>
+          <t>Em Andamento</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Sem sistema de autenticação de usuário implementado (fora do escopo do projeto); validar apenas navegação e leiaute com o público-alvo.</t>
+          <t>Sem sistema de autenticação de usuário implementado (fora do escopo do projeto); validar apenas navegação e leiaute com o público-alvo. Navegação verificada em 03/10/2026 (emulador, API real); falta a avaliação com o público-alvo.</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Não Iniciado</t>
+          <t>Em Andamento</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Cadastro integrado ao endpoint POST /ocorrencias real; ocorrência enviada é persistida no backend.</t>
+          <t>Cadastro integrado ao endpoint POST /ocorrencias real; ocorrência enviada é persistida no backend. Integração com POST /ocorrencias verificada em 03/10/2026 (CT-CAD-001/002/003); falta a avaliação com o público-alvo.</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Não Iniciado</t>
+          <t>Em Andamento</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Listagem consome GET /ocorrencias real (com filtros); validar navegação e leitura pelo público-alvo.</t>
+          <t>Listagem consome GET /ocorrencias real (com filtros); validar navegação e leitura pelo público-alvo. GET /ocorrencias real verificado em 03/10/2026 (CT-LST-001/002, BUG-001 corrigido); falta a avaliação com o público-alvo.</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Não Iniciado</t>
+          <t>Bloqueado</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Marcadores carregados a partir de ocorrências reais retornadas pela API; validar usabilidade da visualização geoespacial.</t>
+          <t>Marcadores carregados a partir de ocorrências reais retornadas pela API; validar usabilidade da visualização geoespacial. Chave do Google Maps restrita a outros certificados (falta cadastrar o SHA-1 do APK de teste); dados da API chegam ao app.</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Não Iniciado</t>
+          <t>Em Andamento</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Dados reais da ocorrência selecionada (via GET /ocorrencias/{id}); validar clareza das informações exibidas.</t>
+          <t>Dados reais da ocorrência selecionada (via GET /ocorrencias/{id}); validar clareza das informações exibidas. GET /ocorrencias/{id} real verificado em 03/10/2026 (CT-DET-001); falta a avaliação com o público-alvo.</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Não Iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Componentes de filtro já implementados na interface (Semana 4), operando sobre dados reais da API.</t>
+          <t>Componentes de filtro já implementados na interface (Semana 4), operando sobre dados reais da API. Filtros de região/período/nível conferidos contra a API em 03/10/2026 (CT-LST-002).</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>Não Iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Alerta local baseado no nível de risco retornado pelo backend real para a ocorrência/região.</t>
+          <t>Alerta local baseado no nível de risco retornado pelo backend real para a ocorrência/região. Notificação disparada com dados reais em 03/10/2026 (CT-NOT-001).</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Não Iniciado</t>
+          <t>Em Andamento</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Tela de configurações/perfil do usuário, com persistência real de preferências.</t>
+          <t>Tela de configurações/perfil do usuário, com persistência real de preferências. Persistência local do perfil verificada em 03/10/2026 (CT-CFG-001); falta a avaliação com o público-alvo.</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="14" customWidth="1" style="6" min="1" max="1"/>
@@ -1850,20 +1850,36 @@
           <t>Formulário envia os dados via POST /ocorrencias e a ocorrência é persistida no backend/banco real.</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>Funcional OK contra a API real: POST /ocorrencias 201, ocorrência nº 319 gravada no PostGIS (nível Alto, id_usuario do perfil) e app abriu os detalhes com o risco. Avaliação de usabilidade com participantes externos ainda pendente.</t>
+        </is>
+      </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>Não Executado</t>
+          <t>Em Execução</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
-      <c r="O11" s="8" t="inlineStr"/>
-      <c r="P11" s="8" t="inlineStr"/>
-      <c r="Q11" s="8" t="inlineStr"/>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/05_cadastro_manual_detalhes.png</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
       <c r="R11" s="8" t="inlineStr">
         <is>
-          <t>Execução planejada para quando o app estiver integrado ao backend real e o protótipo for lançado para teste.</t>
+          <t>Local marcado por GPS (mapa sem chave do Google Maps nesta máquina). Registro de teste apagado do banco depois.</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1936,33 @@
           <t>App impede o envio e sinaliza o campo obrigatório.</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr"/>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Envio bloqueado com a mensagem 'Marque o local da ocorrência antes de enviar.'; nenhum POST chegou à API (log do contêiner).</t>
+        </is>
+      </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>Não Executado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
-      <c r="O12" s="8" t="inlineStr"/>
-      <c r="P12" s="8" t="inlineStr"/>
-      <c r="Q12" s="8" t="inlineStr"/>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/06_cadastro_sem_local.png</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
       <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="36" customHeight="1" s="6">
@@ -1984,17 +2016,33 @@
           <t>Lista exibida de forma legível, com as informações essenciais de cada ocorrência.</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr"/>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Funcional OK: aba Alertas lista as 30 ocorrências de demonstração vindas da API, com fonte, nível, coordenadas e tempo relativo corretos. Avaliação de usabilidade com participantes externos ainda pendente.</t>
+        </is>
+      </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>Não Executado</t>
+          <t>Em Execução</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="8" t="inlineStr"/>
-      <c r="P13" s="8" t="inlineStr"/>
-      <c r="Q13" s="8" t="inlineStr"/>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/03_alertas_api_real.png</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
       <c r="R13" s="8" t="inlineStr"/>
     </row>
     <row r="14" ht="36" customHeight="1" s="6">
@@ -2051,18 +2099,46 @@
           <t>Lista atualizada conforme os filtros escolhidos, refletindo dados reais do backend.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr"/>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>8 combinações de região (Todas/São Caetano do Sul) x período (todo/24 h/7 dias) x nível conferidas contra GET /ocorrencias: todas iguais depois da correção do BUG-001.</t>
+        </is>
+      </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>Não Executado</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
-      <c r="O14" s="8" t="inlineStr"/>
-      <c r="P14" s="8" t="inlineStr"/>
-      <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>BUG-001</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/03_alertas_api_real.png</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t>BUG-001: o contador '&lt;n&gt; ocorrência(s)' ignorava o filtro de nível de risco (a lista filtrava certo). Corrigido em AlertasFragment.kt no mesmo dia e reverificado.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="36" customHeight="1" s="6">
       <c r="A15" s="8" t="inlineStr">
@@ -2116,18 +2192,38 @@
           <t>Mapa carrega corretamente e exibe marcadores nas posições esperadas.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>Dados chegam da API (cartão 'Situação atual': 9 alto, 8 médio, 13 baixo), mas o mapa fica em branco: sem MAPS_API_KEY no android/local.properties desta máquina.</t>
+        </is>
+      </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>Não Executado</t>
+          <t>Bloqueado</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr"/>
-      <c r="O15" s="8" t="inlineStr"/>
-      <c r="P15" s="8" t="inlineStr"/>
-      <c r="Q15" s="8" t="inlineStr"/>
-      <c r="R15" s="8" t="inlineStr"/>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/02_mapa_notificacao_risco.png</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t>Chave do Google Maps recusada ('Authorization failure'): a chave está restrita a certificados Android cadastrados e o APK de teste é assinado com o certificado de depuração desta máquina (SHA-1 35:BA:18:CE:CD:B4:F8:85:29:AD:A2:8B:4B:09:20:C8:57:D3:6B:72). Desbloqueia ao adicionar esse SHA-1 + com.example.alagamentos nas restrições da chave no Google Cloud.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="36" customHeight="1" s="6">
       <c r="A16" s="8" t="inlineStr">
@@ -2181,18 +2277,38 @@
           <t>App navega para a tela de detalhes da ocorrência selecionada.</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr"/>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Não executável sem os marcadores do mapa (ver CT-MAP-001).</t>
+        </is>
+      </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>Não Executado</t>
+          <t>Bloqueado</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="8" t="inlineStr"/>
-      <c r="O16" s="8" t="inlineStr"/>
-      <c r="P16" s="8" t="inlineStr"/>
-      <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>Chave do Google Maps recusada ('Authorization failure'): a chave está restrita a certificados Android cadastrados e o APK de teste é assinado com o certificado de depuração desta máquina (SHA-1 35:BA:18:CE:CD:B4:F8:85:29:AD:A2:8B:4B:09:20:C8:57:D3:6B:72). Desbloqueia ao adicionar esse SHA-1 + com.example.alagamentos nas restrições da chave no Google Cloud.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="36" customHeight="1" s="6">
       <c r="A17" s="8" t="inlineStr">
@@ -2246,18 +2362,46 @@
           <t>Informações completas e legíveis (local, nível de risco, data/hora, descrição).</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr"/>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>Funcional OK: GET /ocorrencias/{id} 200; tela exibe nº, descrição, nível, fonte, data/hora e coordenadas. Avaliação de usabilidade com participantes externos ainda pendente.</t>
+        </is>
+      </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>Não Executado</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
-      <c r="O17" s="8" t="inlineStr"/>
-      <c r="P17" s="8" t="inlineStr"/>
-      <c r="Q17" s="8" t="inlineStr"/>
-      <c r="R17" s="8" t="inlineStr"/>
+          <t>Em Execução</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>BUG-002</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/05_cadastro_manual_detalhes.png</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>BUG-002: com o aparelho em português, as coordenadas saíam '-23,6148, -46,5435' (vírgula decimal confundida com a separadora). Corrigido em 03/10/2026 (sempre ponto decimal) e reverificado em pt-BR.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="36" customHeight="1" s="6">
       <c r="A18" s="8" t="inlineStr">
@@ -2311,20 +2455,36 @@
           <t>App exibe um alerta visual local de risco alto.</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr"/>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>Notificação local disparada com dados reais: '7 novas ocorrências de alagamento — 5 com risco alto. Toque para ver no mapa.' (permissão de notificação concedida).</t>
+        </is>
+      </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>Não Executado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr"/>
-      <c r="O18" s="8" t="inlineStr"/>
-      <c r="P18" s="8" t="inlineStr"/>
-      <c r="Q18" s="8" t="inlineStr"/>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/02_mapa_notificacao_risco.png</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>Alerta local passa a refletir o nível de risco retornado pelo backend real.</t>
+          <t>Limitação conhecida: só verifica com o app aberto (sem serviço em segundo plano).</t>
         </is>
       </c>
     </row>
@@ -2381,20 +2541,36 @@
           <t>Alteração é aceita e persistida (preferência salva no backend/armazenamento real).</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr"/>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>Funcional OK: bairro salvo no perfil e mantido depois de fechar e reabrir o app (cartão em Ajustes: 'Olímpico • São Caetano do Sul'). Avaliação de usabilidade com participantes externos ainda pendente.</t>
+        </is>
+      </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>Não Executado</t>
+          <t>Em Execução</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
-      <c r="O19" s="8" t="inlineStr"/>
-      <c r="P19" s="8" t="inlineStr"/>
-      <c r="Q19" s="8" t="inlineStr"/>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/07_perfil_persistido.png</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>Persistência de preferências validada com o backend/armazenamento real, conforme implementação final.</t>
+          <t>Perfil e preferências ficam só no aparelho (SharedPreferences) — o backend não tem tabela de usuários.</t>
         </is>
       </c>
     </row>
@@ -2451,17 +2627,33 @@
           <t>App navega para a área principal (o login não valida credenciais — não há sistema de autenticação de usuário implementado no projeto).</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr"/>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>Funcional OK: nome e senha quaisquer levam à área principal; sessão mantida ao reabrir o app. Avaliação de usabilidade com participantes externos ainda pendente.</t>
+        </is>
+      </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>Não Executado</t>
+          <t>Em Execução</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="8" t="inlineStr"/>
-      <c r="O20" s="8" t="inlineStr"/>
-      <c r="P20" s="8" t="inlineStr"/>
-      <c r="Q20" s="8" t="inlineStr"/>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/01_login.png</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
           <t>Login não implementa autenticação real; não faz parte do escopo do sistema.</t>
@@ -2469,124 +2661,514 @@
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" s="6">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>CT-API-004</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Backend — API de ocorrências</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>RF-08</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Criar ocorrência sem nivel_risco com a fonte climática principal indisponível</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>P2 - Média</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>API no ar; OpenWeather sem chave ou fora do ar</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>fonte=usuario, sem nivel_risco</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>1. Enviar POST /ocorrencias sem nivel_risco
+2. Observar resposta</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Retornar 503 com mensagem orientando a informar o nível manualmente (não 500 genérico).</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Conforme esperado</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M21" s="8" t="n"/>
       <c r="N21" s="8" t="n"/>
-      <c r="O21" s="8" t="n"/>
-      <c r="P21" s="8" t="n"/>
-      <c r="Q21" s="8" t="n"/>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>backend/tests/test_fusao_climatica_cache.py; docs/evidencias_testes/2026-10-03/04_cadastro_automatico_503.png</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>João (pytest)</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
       <c r="R21" s="8" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1" s="6">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>CT-AHP-003</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Algoritmo de classificação de risco</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>RF-09</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Componente colaborativo a partir de reportes vizinhos</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>P1 - Alta</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Postgres/PostGIS real</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>2 reportes 'Alto' a até 1 km nas últimas 3 h; clima seco (mock)</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>1. Inserir reportes de usuário próximos
+2. Classificar o risco no mesmo ponto</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Score colaborativo calculado (&gt; 0) e registrado em reportes_colaborativos_agregado; com &lt; 2 reportes, componente ausente (fail-safe).</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>Conforme esperado</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n"/>
-      <c r="O22" s="8" t="n"/>
-      <c r="P22" s="8" t="n"/>
-      <c r="Q22" s="8" t="n"/>
-      <c r="R22" s="8" t="n"/>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>backend/tests/test_colaborativo.py (pytest -v)</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>João (pytest)</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>Agregador implementado em 03/10/2026 (servicos/colaborativo.py; T15 seção 6.4).</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="36" customHeight="1" s="6">
-      <c r="A23" s="8" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="8" t="n"/>
-      <c r="L23" s="8" t="n"/>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>CT-API-005</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Backend — API de ocorrências</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>RNF-01/02</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Latência ponta a ponta das leituras e do cadastro</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Desempenho</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>P2 - Média</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>API em contêiner + banco demo e banco de 1 milhão de registros</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>50 requisições por cenário após 5 de aquecimento</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>1. Rodar benchmark/medir_latencia_api.py
+2. Comparar p95 com T19</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Leituras com p95 &lt;= 200 ms; cadastro com nível informado com p95 &lt;= 500 ms.</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>Leituras p95 &lt;= 16,5 ms (1M registros); cadastro manual p95 9,1 ms (API no host) / 259 ms (porta do Docker Desktop); cadastro automático sem cache p95 560 ms e com cache 56,5 ms; GET /risco com cache p95 4,5 ms.</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="8" t="n"/>
-      <c r="O23" s="8" t="n"/>
-      <c r="P23" s="8" t="n"/>
-      <c r="Q23" s="8" t="n"/>
-      <c r="R23" s="8" t="n"/>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>backend/benchmark/resultados/latencia_api_*.csv; docs/T19_criterios_desempenho.md</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>João (benchmark/medir_latencia_api.py)</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="inlineStr">
+        <is>
+          <t>RNF-03 medido em 03/10/2026 com a chave do OpenWeather (clima real).</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="36" customHeight="1" s="6">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>CT-CAD-003</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Cadastro de ocorrência (app)</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>RF-01</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Enviar com nível 'Automático' quando o backend não consegue calcular o risco</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>P2 - Média</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>App integrado à API; OpenWeather indisponível</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Local marcado, nível 'Automático'</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>1. Abrir o cadastro
+2. Marcar o local
+3. Manter 'Automático'
+4. Enviar</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>App mostra mensagem orientando a escolher o nível manualmente e mantém o formulário preenchido.</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Conforme esperado (API respondeu 503; mensagem 'Risco automático indisponível…')</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n"/>
-      <c r="O24" s="8" t="n"/>
-      <c r="P24" s="8" t="n"/>
-      <c r="Q24" s="8" t="n"/>
-      <c r="R24" s="8" t="n"/>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/04_cadastro_automatico_503.png</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t>Mensagem encurtada para caber nas 2 linhas do Toast do Android.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="36" customHeight="1" s="6">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="8" t="n"/>
-      <c r="L25" s="8" t="n"/>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>CT-CAD-004</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Cadastro de ocorrência (app)</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>RF-01 / RF-09</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Enviar com nível 'Automático' com as fontes climáticas disponíveis</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Integração</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>P1 - Alta</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>App integrado à API; OPENWEATHER_API_KEY configurada</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Local marcado por GPS (centro de São Caetano do Sul), nível 'Automático'</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>1. Abrir o cadastro
+2. Marcar o local
+3. Manter 'Automático'
+4. Enviar</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>API classifica pelo AHP com dados climáticos reais, grava a ocorrência e o app abre os detalhes com o nível calculado.</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>POST 201; ocorrência nº 496 gravada com nível 'Baixo' e chuva 0,0 calculados (clima real); app abriu os detalhes.</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M25" s="8" t="n"/>
       <c r="N25" s="8" t="n"/>
-      <c r="O25" s="8" t="n"/>
-      <c r="P25" s="8" t="n"/>
-      <c r="Q25" s="8" t="n"/>
-      <c r="R25" s="8" t="n"/>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/09_cadastro_automatico_toast.png; docs/evidencias_testes/2026-10-03/10_cadastro_automatico_detalhes.png</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>Registro de teste apagado do banco depois.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="36" customHeight="1" s="6">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
-      <c r="L26" s="8" t="n"/>
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>CT-PRV-001</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Previsão / risco atual (app)</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>RF-09</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Consultar o risco de alagamento atual na aba Previsão</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Integração</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>P2 - Média</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>App integrado à API; OPENWEATHER_API_KEY configurada</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Posição do aparelho no centro de São Caetano do Sul</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>1. Abrir a aba Previsão
+2. Comparar com GET /risco para o mesmo ponto</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>Nível, pontuação e cada fonte do cálculo iguais aos da API; fontes sem dado indicadas como 'Sem dado'.</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>App e API iguais: Baixo, 13,7; chuva 0,0 mm/h; pico 12,5 mm em 3 h; ANA e CPTEC 'Sem dado'; poucos relatos.</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n"/>
-      <c r="O26" s="8" t="n"/>
-      <c r="P26" s="8" t="n"/>
-      <c r="Q26" s="8" t="n"/>
-      <c r="R26" s="8" t="n"/>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-03/08_previsao_risco_real.png</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>Sem a chave do OpenWeather, a aba mostra 'Dados climáticos indisponíveis' (verificado antes da chave).</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="36" customHeight="1" s="6">
       <c r="A27" s="8" t="n"/>
@@ -2768,6 +3350,171 @@
       <c r="Q35" s="8" t="n"/>
       <c r="R35" s="8" t="n"/>
     </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:R3"/>

--- a/docs/plano_e_fluxo_de_testes_TCC.xlsx
+++ b/docs/plano_e_fluxo_de_testes_TCC.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>Em Andamento</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Marcadores carregados a partir de ocorrências reais retornadas pela API; validar usabilidade da visualização geoespacial. Chave do Google Maps restrita a outros certificados (falta cadastrar o SHA-1 do APK de teste); dados da API chegam ao app.</t>
+          <t>Marcadores carregados a partir de ocorrências reais retornadas pela API; validar usabilidade da visualização geoespacial. Desbloqueado em 07/10/2026 com o cadastro do SHA-1 do APK de teste na chave do Google Maps: marcadores, painel da ocorrência, navegação para os detalhes e marcação do local no cadastro verificados (CT-MAP-001/002, CT-CAD-001); falta a avaliação com o público-alvo.</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R200"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="14" customWidth="1" style="6" min="1" max="1"/>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>Funcional OK contra a API real: POST /ocorrencias 201, ocorrência nº 319 gravada no PostGIS (nível Alto, id_usuario do perfil) e app abriu os detalhes com o risco. Avaliação de usabilidade com participantes externos ainda pendente.</t>
+          <t>Funcional OK contra a API real, agora com o local marcado por toque no mapa do cadastro: POST /ocorrencias 201, ocorrência gravada no PostGIS com o ponto tocado (POINT(-46.56265 -23.61966), nível Médio, id_usuario do perfil) e app abriu os detalhes. Avaliação de usabilidade com participantes externos ainda pendente.</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -1864,7 +1864,7 @@
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="8" t="inlineStr">
         <is>
-          <t>docs/evidencias_testes/2026-10-03/05_cadastro_manual_detalhes.png</t>
+          <t>docs/evidencias_testes/2026-10-07/04_cadastro_local_no_mapa.png; docs/evidencias_testes/2026-10-07/05_cadastro_enviado_detalhes.png</t>
         </is>
       </c>
       <c r="P11" s="8" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="Q11" s="8" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="R11" s="8" t="inlineStr">
         <is>
-          <t>Local marcado por GPS (mapa sem chave do Google Maps nesta máquina). Registro de teste apagado do banco depois.</t>
+          <t>03/10/2026: local marcado por GPS (mapa sem autorização). 07/10/2026: refeito marcando o local no mapa, depois do cadastro do SHA-1. Registros de teste apagados do banco depois.</t>
         </is>
       </c>
     </row>
@@ -2194,19 +2194,19 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Dados chegam da API (cartão 'Situação atual': 9 alto, 8 médio, 13 baixo), mas o mapa fica em branco: sem MAPS_API_KEY no android/local.properties desta máquina.</t>
+          <t>Funcional OK: mapa do Google carregado (sem 'Authorization failure' no logcat) com as 30 ocorrências de demonstração da API como marcadores coloridos por nível (cartão 'Situação atual': 9 alto, 8 médio, 13 baixo) e enquadramento em São Caetano do Sul. Posição conferida: marcador da ocorrência nº 879 em -23.6124, -46.5754, igual a GET /ocorrencias/879. Avaliação de usabilidade com participantes externos ainda pendente.</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>Em Execução</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="8" t="inlineStr">
         <is>
-          <t>docs/evidencias_testes/2026-10-03/02_mapa_notificacao_risco.png</t>
+          <t>docs/evidencias_testes/2026-10-07/01_mapa_marcadores.png</t>
         </is>
       </c>
       <c r="P15" s="8" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="Q15" s="8" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>Chave do Google Maps recusada ('Authorization failure'): a chave está restrita a certificados Android cadastrados e o APK de teste é assinado com o certificado de depuração desta máquina (SHA-1 35:BA:18:CE:CD:B4:F8:85:29:AD:A2:8B:4B:09:20:C8:57:D3:6B:72). Desbloqueia ao adicionar esse SHA-1 + com.example.alagamentos nas restrições da chave no Google Cloud.</t>
+          <t>03/10/2026: Bloqueado (chave do Google Maps restrita a outros certificados). Desbloqueado em 07/10/2026 com o cadastro do SHA-1 do certificado de depuração do notebook de testes nas restrições da chave.</t>
         </is>
       </c>
     </row>
@@ -2279,19 +2279,19 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Não executável sem os marcadores do mapa (ver CT-MAP-001).</t>
+          <t>Funcional OK: toque no marcador abre o painel da ocorrência (descrição, coordenadas, nível, fonte e data/hora) e o botão 'Ver detalhes' abre a tela de detalhes da mesma ocorrência (nº 879, dados iguais aos de GET /ocorrencias/879). Avaliação de usabilidade com participantes externos ainda pendente.</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>Em Execução</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/evidencias_testes/2026-10-07/02_mapa_marcador_selecionado.png; docs/evidencias_testes/2026-10-07/03_mapa_para_detalhes.png</t>
         </is>
       </c>
       <c r="P16" s="8" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="Q16" s="8" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>Chave do Google Maps recusada ('Authorization failure'): a chave está restrita a certificados Android cadastrados e o APK de teste é assinado com o certificado de depuração desta máquina (SHA-1 35:BA:18:CE:CD:B4:F8:85:29:AD:A2:8B:4B:09:20:C8:57:D3:6B:72). Desbloqueia ao adicionar esse SHA-1 + com.example.alagamentos nas restrições da chave no Google Cloud.</t>
+          <t>A navegação tem dois passos (marcador → painel → 'Ver detalhes'), não um: o painel permite conferir a ocorrência antes de sair do mapa. Desbloqueado em 07/10/2026 (ver CT-MAP-001).</t>
         </is>
       </c>
     </row>
@@ -3166,29 +3166,94 @@
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>Sem a chave do OpenWeather, a aba mostra 'Dados climáticos indisponíveis' (verificado antes da chave).</t>
+          <t>Sem a chave do OpenWeather, a aba mostra 'Dados climáticos indisponíveis' (verificado antes da chave). Em 03/10/2026 o painel ainda mostrava o CPTEC; desde 06/10/2026 a linha é 'Previsão INMET' (ver CT-PRV-002).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" s="6">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="8" t="n"/>
-      <c r="L27" s="8" t="n"/>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>CT-PRV-002</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Previsão / risco atual (app)</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>RF-09</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Exibir os avisos oficiais do INMET e aplicar o piso de classificação</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Integração</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>P2 - Média</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>App integrado à API; INMET (apiprevmet3) respondendo</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Posição no centro de São Caetano do Sul; avisos ativos do INMET no dia (IBGE 3548807)</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>1. Abrir a aba Previsão
+2. Comparar avisos, classe e piso com GET /risco para o mesmo ponto</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>Avisos vigentes do município listados com evento, severidade, validade e riscos; classe final igual à da API. Aviso de chuva 'Perigo' eleva a classe a no mínimo Médio e 'Grande Perigo' a Alto (o app explica a elevação); 'Perigo Potencial' não altera a classe.</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>App e API iguais: aviso 'Tempestade · Perigo Potencial' (07/10 00:00 a 23:59) exibido com o texto de riscos do INMET; classe Baixo, pontuação 0,0, sem piso (correto para Perigo Potencial); previsão INMET 'Muitas nuvens com chuva isolada'.</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M27" s="8" t="n"/>
       <c r="N27" s="8" t="n"/>
-      <c r="O27" s="8" t="n"/>
-      <c r="P27" s="8" t="n"/>
-      <c r="Q27" s="8" t="n"/>
-      <c r="R27" s="8" t="n"/>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-07/06_previsao_avisos_inmet.png</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>O piso com 'Perigo'/'Grande Perigo' depende de haver aviso desse nível no dia; a regra é coberta por backend/tests/test_inmet.py (pytest). INMET no lugar do CPTEC desde 06/10/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="36" customHeight="1" s="6">
       <c r="A28" s="8" t="n"/>
@@ -3350,171 +3415,6 @@
       <c r="Q35" s="8" t="n"/>
       <c r="R35" s="8" t="n"/>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:R3"/>

--- a/docs/plano_e_fluxo_de_testes_TCC.xlsx
+++ b/docs/plano_e_fluxo_de_testes_TCC.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" style="6" min="1" max="1"/>
@@ -500,7 +500,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Backend (API REST FastAPI de ocorrências + algoritmo de classificação de risco AHP) e aplicativo Android (telas de login, cadastro de ocorrência, listagem/histórico, mapa, detalhes da ocorrência, filtros, notificações locais e configurações/perfil, em XML/Views)</t>
+          <t>Backend (API REST FastAPI de ocorrências + algoritmo de classificação de risco AHP) e aplicativo Android (telas de login, cadastro de ocorrência, listagem/histórico, mapa, detalhes da ocorrência, filtros, risco atual com avisos do INMET (aba Previsão), notificações locais e configurações/perfil, em XML/Views)</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Verificar se as funcionalidades implementadas até a Semana 10 (backend de ocorrências + classificação de risco, e telas Android do protótipo) funcionam conforme especificado e se a interface é compreensível e utilizável pelo público-alvo (moradores de São Caetano do Sul e demais participantes recrutados), antes da integração final entre app e backend real.</t>
+          <t>Verificar se as funcionalidades do sistema (backend de ocorrências, classificação de risco e aplicativo Android integrado à API real) funcionam conforme especificado e se a interface é compreensível e utilizável pelo público-alvo (moradores de São Caetano do Sul e demais participantes recrutados). Versão 1.0 (13/09/2026) escrita antes da integração entre app e backend, concluída em 03/10/2026.</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Backend: POST/GET /ocorrencias (criar, listar com filtros de fonte/nível de risco/período/região, obter por id) e o cálculo automático de nivel_risco via fusao_climatica + algoritmo AHP. Android (aplicativo integrado ao backend real): telas de login, cadastro de ocorrência, listagem/histórico, mapa (Google Maps SDK), detalhes da ocorrência, filtros de região/período, notificações locais de risco alto e configurações/perfil, todas consumindo dados reais da API.</t>
+          <t>Backend: POST/GET /ocorrencias (criar, listar com filtros de fonte/nível de risco/período/região, obter por id) e o cálculo automático de nivel_risco via fusao_climatica + algoritmo AHP; GET /risco (risco atual num ponto, com avisos do INMET como piso). Android (aplicativo integrado ao backend real): telas de login, cadastro de ocorrência, listagem/histórico, mapa (Google Maps SDK), detalhes da ocorrência, filtros de região/período, aba Previsão (risco atual e avisos do INMET), notificações locais de risco alto e configurações/perfil, todas consumindo dados reais da API.</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Cadastro integrado ao endpoint POST /ocorrencias real; ocorrência enviada é persistida no backend. Integração com POST /ocorrencias verificada em 03/10/2026 (CT-CAD-001/002/003); falta a avaliação com o público-alvo.</t>
+          <t>Cadastro integrado ao endpoint POST /ocorrencias real; ocorrência enviada é persistida no backend. Integração com POST /ocorrencias verificada em 03/10/2026 (CT-CAD-001/002/003); falta a avaliação com o público-alvo. 07/10/2026: busca por endereço, mapa arrastável e bloqueio de locais fora de São Caetano do Sul verificados (CT-CAD-005/006/007).</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" s="6">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Configurações / perfil do usuário</t>
@@ -1193,6 +1193,48 @@
       <c r="H43" s="8" t="inlineStr">
         <is>
           <t>Tela de configurações/perfil do usuário, com persistência real de preferências. Persistência local do perfil verificada em 03/10/2026 (CT-CFG-001); falta a avaliação com o público-alvo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" s="6">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Previsão / risco atual (GET /risco + avisos do INMET)</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>RF-09</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Funcional / Usabilidade</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>P2 - Média</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>João</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>Em Andamento</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Aba Previsão com o risco AHP atual, os dados do cálculo e os avisos oficiais do INMET (piso da classe). Conferida com GET /risco em 03/10 e 07/10/2026 (CT-PRV-001/002); ícones ⓘ com a origem dos dados em 07/10/2026 (CT-PRV-003); falta a avaliação com o público-alvo.</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2178,7 @@
       </c>
       <c r="R14" s="8" t="inlineStr">
         <is>
-          <t>BUG-001: o contador '&lt;n&gt; ocorrência(s)' ignorava o filtro de nível de risco (a lista filtrava certo). Corrigido em AlertasFragment.kt no mesmo dia e reverificado.</t>
+          <t>BUG-001: o contador '&lt;n&gt; ocorrência(s)' ignorava o filtro de nível de risco (a lista filtrava certo). Corrigido em AlertasFragment.kt no mesmo dia e reverificado. Desde 07/10/2026 a lista abre em 'Últimas 24 h' (antes, 'Todo o período').</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2263,7 @@
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>03/10/2026: Bloqueado (chave do Google Maps restrita a outros certificados). Desbloqueado em 07/10/2026 com o cadastro do SHA-1 do certificado de depuração do notebook de testes nas restrições da chave.</t>
+          <t>03/10/2026: Bloqueado (chave do Google Maps restrita a outros certificados). Desbloqueado em 07/10/2026 com o cadastro do SHA-1 do certificado de depuração do notebook de testes nas restrições da chave. Execução com as 30 ocorrências; desde 07/10/2026 o mapa mostra só as das últimas 24 h (CT-MAP-003).</t>
         </is>
       </c>
     </row>
@@ -3256,124 +3298,519 @@
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" s="6">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="8" t="n"/>
-      <c r="L28" s="8" t="n"/>
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>CT-CAD-005</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Cadastro de ocorrência (app)</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>RF-01</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Marcar o local da ocorrência digitando o endereço</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>P2 - Média</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>App integrado à API; internet (geocodificador do Android)</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>'Rua Alegre, 100', 'Rua Baraldi, 800' e o bairro 'Santa Paula' (São Caetano do Sul)</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>1. Abrir o cadastro
+2. Digitar o endereço no campo de busca
+3. Tocar na lupa (ou Buscar/Enter)
+4. Enviar a ocorrência</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>O pino vai para o endereço, o mapa se move até ele e a linha abaixo do mapa mostra o endereço encontrado; a ocorrência é gravada nesse ponto.</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Os 3 endereços foram encontrados em São Caetano do Sul (ex.: 'Rua Alegre, 100 - Santa Paula (-23.61809, -46.55506)'); envio com nível Médio: POST 201, ponto gravado no PostGIS igual ao do endereço (POINT(-46.55506 -23.61809)).</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M28" s="8" t="n"/>
       <c r="N28" s="8" t="n"/>
-      <c r="O28" s="8" t="n"/>
-      <c r="P28" s="8" t="n"/>
-      <c r="Q28" s="8" t="n"/>
-      <c r="R28" s="8" t="n"/>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-07/12_cadastro_busca_endereco.png; docs/evidencias_testes/2026-10-07/13_cadastro_busca_enviado.png</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>Busca em duas etapas: com ', São Caetano do Sul - SP' no texto e, sem resultado, o texto como foi digitado. Sem o nome da cidade, o geocodificador não achava 'Rua Alegre, 100'. Registro de teste apagado do banco depois.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="36" customHeight="1" s="6">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
-      <c r="L29" s="8" t="n"/>
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>CT-CAD-006</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Cadastro de ocorrência (app)</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>RF-01</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Impedir local fora de São Caetano do Sul (endereço, toque no mapa ou GPS)</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>P1 - Alta</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>App integrado à API; internet (geocodificador do Android)</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>'Avenida Paulista, 1000' (São Paulo); 'Avenida Industrial, 600, Santo Andre'; toque no mapa em São Paulo; texto inexistente 'Qwxyz Zzkkq 99999'</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>1. Buscar um endereço de outra cidade
+2. Arrastar o mapa para fora do município e tocar
+3. Buscar um texto que não existe</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>Endereço ou toque fora do município: aviso 'Localização informada não pertence a São Caetano do Sul' e nenhum pino aceito; texto inexistente: 'Endereço não encontrado' no campo, com a lupa ainda disponível.</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Conforme esperado: aviso 'Local fora da área' para Av. Paulista, Av. Industrial (Santo André) e para o toque em São Paulo (busca reversa: 'Rua Guaramembé, 510 - Umarizal, São Paulo'), com o pino removido; texto inexistente: 'Endereço não encontrado' e a lupa continua visível.</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M29" s="8" t="n"/>
       <c r="N29" s="8" t="n"/>
-      <c r="O29" s="8" t="n"/>
-      <c r="P29" s="8" t="n"/>
-      <c r="Q29" s="8" t="n"/>
-      <c r="R29" s="8" t="n"/>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-07/09_cadastro_busca_nao_encontrado.png; docs/evidencias_testes/2026-10-07/10_cadastro_busca_fora_da_cidade.png; docs/evidencias_testes/2026-10-07/11_cadastro_toque_fora_da_cidade.png</t>
+        </is>
+      </c>
+      <c r="P29" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>A cidade vem do geocodificador (subAdminArea/locality); sem resposta dele, vale o retângulo aproximado do município. Regra em Municipio.kt, com testes de JVM. Até 07/10/2026 um ponto fora só gerava um aviso e o envio era permitido. Durante a validação, o Material trocava a lupa pelo ícone de erro — corrigido (errorIconDrawable nulo).</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="36" customHeight="1" s="6">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
-      <c r="L30" s="8" t="n"/>
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>CT-CAD-007</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Cadastro de ocorrência (app)</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>RF-01</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Mover o mapa do cadastro arrastando, sem rolar a tela</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>P2 - Média</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Tela de cadastro aberta</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Arrasto horizontal e diagonal sobre o mapa</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>1. Arrastar o dedo sobre o mapa
+2. Observar o mapa e a posição da tela</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>O mapa se move com o dedo e a tela não rola; tocar sem arrastar continua marcando o pino.</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>Conforme esperado: o mapa se moveu (de Santa Paula até São Paulo em três arrastos) e a posição do campo de busca na tela não mudou; toques continuaram marcando o pino.</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M30" s="8" t="n"/>
       <c r="N30" s="8" t="n"/>
-      <c r="O30" s="8" t="n"/>
-      <c r="P30" s="8" t="n"/>
-      <c r="Q30" s="8" t="n"/>
-      <c r="R30" s="8" t="n"/>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-07/11_cadastro_toque_fora_da_cidade.png</t>
+        </is>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>Antes de 07/10/2026 os gestos do mapa ficavam desligados (o arrasto rolava a tela). Moldura MapaArrastavel.kt impede a rolagem da tela enquanto o dedo está no mapa; girar e inclinar seguem desligados.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="36" customHeight="1" s="6">
-      <c r="A31" s="8" t="n"/>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="8" t="n"/>
-      <c r="L31" s="8" t="n"/>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>CT-PRV-003</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Previsão / risco atual (app)</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>RF-09</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Consultar a origem de cada dado e a explicação do cálculo pelos ícones de informação</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Usabilidade</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>P3 - Baixa</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Aba Previsão com dados</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>1. Tocar no ícone ⓘ ao lado de cada dado de 'O que entrou no cálculo'
+2. Tocar no ícone ⓘ do cartão de risco</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Cada ícone abre um cartão com a fonte do dado (ANA com o nome por extenso; previsão do INMET como apenas descritiva) e o do cartão de risco explica o cálculo.</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>Funcional OK: os 5 cartões de fonte e o cartão 'Como o risco é calculado' abrem com o texto previsto; rótulos sem a fonte entre parênteses. Avaliação com participantes externos pendente.</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>Em Execução</t>
+        </is>
+      </c>
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n"/>
-      <c r="O31" s="8" t="n"/>
-      <c r="P31" s="8" t="n"/>
-      <c r="Q31" s="8" t="n"/>
-      <c r="R31" s="8" t="n"/>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-07/07_previsao_info_fonte_ana.png; docs/evidencias_testes/2026-10-07/08_previsao_info_risco.png</t>
+        </is>
+      </c>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>Pedido do João em 07/10/2026: a origem dos dados e a explicação do cálculo saíram do texto da tela e foram para ícones ⓘ (área de toque de 48 dp, com descrição para leitor de tela).</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="36" customHeight="1" s="6">
-      <c r="A32" s="8" t="n"/>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="n"/>
-      <c r="L32" s="8" t="n"/>
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>CT-API-006</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Backend — API de ocorrências</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>RF-08</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Recusar ocorrência fora de São Caetano do Sul</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>P1 - Alta</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>API no ar</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Santo André (-23.6639, -46.5383) e Fortaleza (-3.7319, -38.5267)</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>1. Enviar POST /ocorrencias com um ponto fora da área monitorada
+2. Observar a resposta e a listagem</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Retornar 422 com mensagem citando São Caetano do Sul; nada é gravado.</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>Conforme esperado: 422 'Localização fora de São Caetano do Sul (área monitorada pelo sistema).' nos dois pontos, listagem vazia; também conferido ao vivo contra a API em contêiner.</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="n"/>
-      <c r="O32" s="8" t="n"/>
-      <c r="P32" s="8" t="n"/>
-      <c r="Q32" s="8" t="n"/>
-      <c r="R32" s="8" t="n"/>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>backend/tests/test_ocorrencias_api.py::test_criar_ocorrencia_fora_de_sao_caetano_e_422</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>João (pytest)</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>Validação no contrato de entrada (api/schemas.py), com o retângulo aproximado do município (constants.AREA_SAO_CAETANO_DO_SUL, o mesmo do app). Antes, só o app recusava. Os testes que usavam Santo André e Fortaleza passaram a usar pontos de São Caetano do Sul.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="36" customHeight="1" s="6">
-      <c r="A33" s="8" t="n"/>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
-      <c r="L33" s="8" t="n"/>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>CT-MAP-003</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>RF-03</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Mostrar no mapa só as ocorrências ativas (24 h) e esmaecer as com mais de 3 h</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>P1 - Alta</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>App integrado à API; ocorrências de demonstração recarregadas no dia</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>30 ocorrências de demonstração: 10 nas últimas 24 h (as demais de 1 a 10 dias atrás)</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>1. Abrir o mapa
+2. Comparar marcadores e 'Situação atual' com GET /ocorrencias?data_inicio=&lt;agora - 24 h&gt;
+3. Observar os marcadores com mais e menos de 3 h
+4. Abrir a aba Alertas</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Mapa, 'Situação atual' e faixa de alerta contam só as ocorrências das últimas 24 h; as com mais de 3 h aparecem esmaecidas; a aba Alertas abre em 'Últimas 24 h' e mantém o histórico nos outros períodos.</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Conforme esperado: 10 marcadores (5 alto, 2 médio, 3 baixo), iguais à consulta da API com data_inicio; faixa '5 ocorrência(s) com risco alto nas últimas 24 h' (antes contava as 30, de até 10 dias, como '9 com risco alto'); marcadores com mais de 3 h esmaecidos; Alertas abriu em 'Últimas 24 h' com 10 ocorrências.</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="n"/>
-      <c r="O33" s="8" t="n"/>
-      <c r="P33" s="8" t="n"/>
-      <c r="Q33" s="8" t="n"/>
-      <c r="R33" s="8" t="n"/>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-07/14_mapa_ultimas_24h_esmaecidas.png; docs/capturas/02_alertas.png</t>
+        </is>
+      </c>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
+          <t>João (automação adb no emulador)</t>
+        </is>
+      </c>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t>Pedido do João em 07/10/2026: ocorrências não podem ficar no mapa para sempre. Nada é apagado do banco. Janelas em JanelaOcorrencia (Ocorrencia.kt): 24 h (mesma das notificações) e 3 h (mesma do componente colaborativo do AHP), com teste de JVM.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="36" customHeight="1" s="6">
       <c r="A34" s="8" t="n"/>

--- a/docs/plano_e_fluxo_de_testes_TCC.xlsx
+++ b/docs/plano_e_fluxo_de_testes_TCC.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Backend: POST/GET /ocorrencias (criar, listar com filtros de fonte/nível de risco/período/região, obter por id) e o cálculo automático de nivel_risco via fusao_climatica + algoritmo AHP; GET /risco (risco atual num ponto, com avisos do INMET como piso). Android (aplicativo integrado ao backend real): telas de login, cadastro de ocorrência, listagem/histórico, mapa (Google Maps SDK), detalhes da ocorrência, filtros de região/período, aba Previsão (risco atual e avisos do INMET), notificações locais de risco alto e configurações/perfil, todas consumindo dados reais da API.</t>
+          <t>Backend: POST/GET /ocorrencias (criar, listar com filtros de fonte/nível de risco/período/região, obter por id) e o cálculo automático de nivel_risco via fusao_climatica (OpenWeather + Open-Meteo, maior valor) + algoritmo AHP de três critérios; GET /risco (risco atual num ponto, com avisos do INMET como piso). Android (aplicativo integrado ao backend real): telas de login, cadastro de ocorrência, listagem/histórico, mapa (Google Maps SDK), detalhes da ocorrência, filtros de região/período, aba Previsão (risco atual e avisos do INMET), notificações locais de risco alto e configurações/perfil, todas consumindo dados reais da API.</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Fora do escopo desta rodada: autenticação real de usuário (o projeto não implementa cadastro/login de contas — a tela de login não valida credenciais); testes de carga/desempenho formais (tratados à parte no benchmark de indexação espacial, Semanas 7–11); fontes ANA e estação USCS (aguardando acesso/decisão, ver docs/T_arquitetura_fontes_dados_final.md).</t>
+          <t>Fora do escopo desta rodada: autenticação real de usuário (o projeto não implementa cadastro/login de contas — a tela de login não valida credenciais); testes de carga/desempenho formais (tratados à parte no benchmark de indexação espacial, Semanas 7–11); fontes ANA e estação USCS (retiradas do projeto em 16/10/2026 por falta de acesso, ver docs/T_arquitetura_fontes_dados_final.md).</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Dependência de resposta da ANA para validar as 4 fontes climáticas em produção (ver CRONOGRAMA_STATUS.md); disponibilidade dos participantes externos; ambiente de backend real (Docker/Postgres) precisa estar acessível e populado com massa de teste antes da aplicação.</t>
+          <t>Dependência de serviços externos sem garantia de disponibilidade (OpenWeather, Open-Meteo, INMET); disponibilidade dos participantes externos; ambiente de backend real (Docker/Postgres) precisa estar acessível e populado com massa de teste antes da aplicação.</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>algoritmo_risco.py + fusao_climatica.py testados com dado real (Santo André, score 4.2) e com ANA disponível/indisponível; ver T15_algoritmo_risco_fundamentacao.md.</t>
+          <t>algoritmo_risco.py + fusao_climatica.py testados com dado real (Santo André, score 4.2) e com ANA disponível/indisponível; ver T15_algoritmo_risco_fundamentacao.md. 16/10/2026: três critérios (54/30/16) e fusão OpenWeather × Open-Meteo, verificados ao vivo e por pytest (CT-AHP-004).</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="14" customWidth="1" style="6" min="1" max="1"/>
@@ -1837,7 +1837,11 @@
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="R10" s="8" t="inlineStr"/>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>Obsoleto desde 16/10/2026: a ANA foi retirada do projeto e o modelo passou a ter três critérios (ver CT-AHP-004).</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="36" customHeight="1" s="6">
       <c r="A11" s="8" t="inlineStr">
@@ -2781,7 +2785,11 @@
           <t>03/10/2026</t>
         </is>
       </c>
-      <c r="R21" s="8" t="n"/>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>Desde 16/10/2026 o 503 só ocorre com OpenWeather e Open-Meteo indisponíveis; sem o OpenWeather, o cálculo usa a Open-Meteo (tests/test_fusao_climatica_cache.py).</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="36" customHeight="1" s="6">
       <c r="A22" s="8" t="inlineStr">
@@ -3813,24 +3821,91 @@
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" s="6">
-      <c r="A34" s="8" t="n"/>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
-      <c r="L34" s="8" t="n"/>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>CT-AHP-004</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Algoritmo de classificação de risco</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>RF-09</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Fundir OpenWeather e Open-Meteo e classificar com os pesos de três critérios</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Integração</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>P1 - Alta</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>API no ar; OpenWeather e Open-Meteo respondendo (cenários de falha com fontes simuladas)</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Centro de São Caetano do Sul (-23.6229, -46.5548), 16/10/2026, com chuva fraca</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>1. GET /risco no ponto
+2. Conferir o valor de cada fonte, o valor usado e a divergência
+3. Recalcular o score com os pesos 54/30/16
+4. Simular a falha de uma e das duas fontes (pytest)</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>Valor usado = maior entre as fontes; divergência só quando caem em faixas diferentes da OMM; score igual ao cálculo manual; com uma fonte, usa a disponível; sem nenhuma, 503.</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>Conforme esperado: chuva atual OpenWeather 1,02 × Open-Meteo 2,0 mm/h → 2,0 (mesma faixa, sem divergência); previsão 4,07 × 5,1 mm em 3 h → 5,1; score 18,9 (20,0 × 64,3% + 17,0 × 35,7%, sem relatos) = Baixo; app mostra os dois valores no cartão ⓘ. Falhas: só Open-Meteo → calcula; nenhuma → 503.</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
       <c r="M34" s="8" t="n"/>
       <c r="N34" s="8" t="n"/>
-      <c r="O34" s="8" t="n"/>
-      <c r="P34" s="8" t="n"/>
-      <c r="Q34" s="8" t="n"/>
-      <c r="R34" s="8" t="n"/>
+      <c r="O34" s="8" t="inlineStr">
+        <is>
+          <t>docs/evidencias_testes/2026-10-16/01_previsao_tres_criterios.png; docs/evidencias_testes/2026-10-16/02_previsao_info_fusao_chuva.png; backend/tests/test_open_meteo.py; backend/tests/test_fusao_climatica_latencia.py</t>
+        </is>
+      </c>
+      <c r="P34" s="8" t="inlineStr">
+        <is>
+          <t>João (API ao vivo, emulador e pytest)</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t>Ajuste de escopo de 16/10/2026 (decisão do grupo): ANA e estação da USCS retiradas; Open-Meteo como segunda fonte; pesos do autovetor (CR = 0,0079), sem ajuste manual. Ver T15 §8.2.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="36" customHeight="1" s="6">
       <c r="A35" s="8" t="n"/>
@@ -3852,6 +3927,50 @@
       <c r="Q35" s="8" t="n"/>
       <c r="R35" s="8" t="n"/>
     </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:R3"/>

--- a/docs/plano_e_fluxo_de_testes_TCC.xlsx
+++ b/docs/plano_e_fluxo_de_testes_TCC.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>Em Andamento</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Sem sistema de autenticação de usuário implementado (fora do escopo do projeto); validar apenas navegação e leiaute com o público-alvo. Navegação verificada em 03/10/2026 (emulador, API real); falta a avaliação com o público-alvo.</t>
+          <t>Sem sistema de autenticação de usuário implementado (fora do escopo do projeto); validar apenas navegação e leiaute com o público-alvo. Navegação verificada em 03/10/2026 (emulador, API real); falta a avaliação com o público-alvo. 29/10/2026: avaliação de usabilidade concluída (12 participantes, média 4,79 em 5), ver docs/evidencias_testes/usabilidade/.</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Em Andamento</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Cadastro integrado ao endpoint POST /ocorrencias real; ocorrência enviada é persistida no backend. Integração com POST /ocorrencias verificada em 03/10/2026 (CT-CAD-001/002/003); falta a avaliação com o público-alvo. 07/10/2026: busca por endereço, mapa arrastável e bloqueio de locais fora de São Caetano do Sul verificados (CT-CAD-005/006/007).</t>
+          <t>Cadastro integrado ao endpoint POST /ocorrencias real; ocorrência enviada é persistida no backend. Integração com POST /ocorrencias verificada em 03/10/2026 (CT-CAD-001/002/003); falta a avaliação com o público-alvo. 07/10/2026: busca por endereço, mapa arrastável e bloqueio de locais fora de São Caetano do Sul verificados (CT-CAD-005/006/007). 29/10/2026: avaliação de usabilidade concluída (12 participantes, média 4,79 em 5), ver docs/evidencias_testes/usabilidade/.</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Em Andamento</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Listagem consome GET /ocorrencias real (com filtros); validar navegação e leitura pelo público-alvo. GET /ocorrencias real verificado em 03/10/2026 (CT-LST-001/002, BUG-001 corrigido); falta a avaliação com o público-alvo.</t>
+          <t>Listagem consome GET /ocorrencias real (com filtros); validar navegação e leitura pelo público-alvo. GET /ocorrencias real verificado em 03/10/2026 (CT-LST-001/002, BUG-001 corrigido); falta a avaliação com o público-alvo. 29/10/2026: avaliação de usabilidade concluída (12 participantes, média 4,79 em 5), ver docs/evidencias_testes/usabilidade/.</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Em Andamento</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Marcadores carregados a partir de ocorrências reais retornadas pela API; validar usabilidade da visualização geoespacial. Desbloqueado em 07/10/2026 com o cadastro do SHA-1 do APK de teste na chave do Google Maps: marcadores, painel da ocorrência, navegação para os detalhes e marcação do local no cadastro verificados (CT-MAP-001/002, CT-CAD-001); falta a avaliação com o público-alvo.</t>
+          <t>Marcadores carregados a partir de ocorrências reais retornadas pela API; validar usabilidade da visualização geoespacial. Desbloqueado em 07/10/2026 com o cadastro do SHA-1 do APK de teste na chave do Google Maps: marcadores, painel da ocorrência, navegação para os detalhes e marcação do local no cadastro verificados (CT-MAP-001/002, CT-CAD-001); falta a avaliação com o público-alvo. 29/10/2026: avaliação de usabilidade concluída (12 participantes, média 4,79 em 5), ver docs/evidencias_testes/usabilidade/.</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>Em Andamento</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Dados reais da ocorrência selecionada (via GET /ocorrencias/{id}); validar clareza das informações exibidas. GET /ocorrencias/{id} real verificado em 03/10/2026 (CT-DET-001); falta a avaliação com o público-alvo.</t>
+          <t>Dados reais da ocorrência selecionada (via GET /ocorrencias/{id}); validar clareza das informações exibidas. GET /ocorrencias/{id} real verificado em 03/10/2026 (CT-DET-001); falta a avaliação com o público-alvo. 29/10/2026: avaliação de usabilidade concluída (12 participantes, média 4,79 em 5), ver docs/evidencias_testes/usabilidade/.</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Em Andamento</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Tela de configurações/perfil do usuário, com persistência real de preferências. Persistência local do perfil verificada em 03/10/2026 (CT-CFG-001); falta a avaliação com o público-alvo.</t>
+          <t>Tela de configurações/perfil do usuário, com persistência real de preferências. Persistência local do perfil verificada em 03/10/2026 (CT-CFG-001); falta a avaliação com o público-alvo. 29/10/2026: avaliação de usabilidade concluída (12 participantes, média 4,79 em 5), ver docs/evidencias_testes/usabilidade/.</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>Em Andamento</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Aba Previsão com o risco AHP atual, os dados do cálculo e os avisos oficiais do INMET (piso da classe). Conferida com GET /risco em 03/10 e 07/10/2026 (CT-PRV-001/002); ícones ⓘ com a origem dos dados em 07/10/2026 (CT-PRV-003); falta a avaliação com o público-alvo.</t>
+          <t>Aba Previsão com o risco AHP atual, os dados do cálculo e os avisos oficiais do INMET (piso da classe). Conferida com GET /risco em 03/10 e 07/10/2026 (CT-PRV-001/002); ícones ⓘ com a origem dos dados em 07/10/2026 (CT-PRV-003); falta a avaliação com o público-alvo. 29/10/2026: avaliação de usabilidade concluída (12 participantes, média 4,79 em 5), ver docs/evidencias_testes/usabilidade/.</t>
         </is>
       </c>
     </row>
@@ -1898,34 +1898,34 @@
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>Funcional OK contra a API real, agora com o local marcado por toque no mapa do cadastro: POST /ocorrencias 201, ocorrência gravada no PostGIS com o ponto tocado (POINT(-46.56265 -23.61966), nível Médio, id_usuario do perfil) e app abriu os detalhes. Avaliação de usabilidade com participantes externos ainda pendente.</t>
+          <t>Parte funcional aprovada em emulador (ver evidências anteriores). Avaliação de usabilidade por questionário sobre as capturas das telas (Google Forms, 12 participantes que aceitaram o termo, 17 a 21/10/2026): tela Cadastro com média 4,77 em 5 (critério ≥ 4). 9 de 12 entenderam a diferença entre Automático e escolher o nível (2 em parte, 1 não). Melhoria aplicada em 29/10/2026: Explicação dos dois modos sempre visível; texto que citava pluviômetros corrigido.</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>Em Execução</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="8" t="inlineStr">
         <is>
-          <t>docs/evidencias_testes/2026-10-07/04_cadastro_local_no_mapa.png; docs/evidencias_testes/2026-10-07/05_cadastro_enviado_detalhes.png</t>
+          <t>docs/evidencias_testes/2026-10-07/04_cadastro_local_no_mapa.png; docs/evidencias_testes/2026-10-07/05_cadastro_enviado_detalhes.png; docs/evidencias_testes/usabilidade/analise_usabilidade_2026-10-29.md; docs/evidencias_testes/usabilidade/respostas_formulario_2026-10.csv</t>
         </is>
       </c>
       <c r="P11" s="8" t="inlineStr">
         <is>
-          <t>João (automação adb no emulador)</t>
+          <t>Grupo (formulário) e João (análise e melhorias)</t>
         </is>
       </c>
       <c r="Q11" s="8" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="R11" s="8" t="inlineStr">
         <is>
-          <t>03/10/2026: local marcado por GPS (mapa sem autorização). 07/10/2026: refeito marcando o local no mapa, depois do cadastro do SHA-1. Registros de teste apagados do banco depois.</t>
+          <t>03/10/2026: local marcado por GPS (mapa sem autorização). 07/10/2026: refeito marcando o local no mapa, depois do cadastro do SHA-1. Registros de teste apagados do banco depois. Avaliação sem uso do app pelos participantes (só as telas) e amostra de conveniência (familiares e amigos): ver limitações em T16_secao_metodologia_testes.md.</t>
         </is>
       </c>
     </row>
@@ -2064,32 +2064,36 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>Funcional OK: aba Alertas lista as 30 ocorrências de demonstração vindas da API, com fonte, nível, coordenadas e tempo relativo corretos. Avaliação de usabilidade com participantes externos ainda pendente.</t>
+          <t>Parte funcional aprovada em emulador (ver evidências anteriores). Avaliação de usabilidade por questionário sobre as capturas das telas (Google Forms, 12 participantes que aceitaram o termo, 17 a 21/10/2026): tela Alertas com média 4,62 em 5 (critério ≥ 4). 12 de 12 acharam os filtros fáceis de combinar.</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>Em Execução</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="8" t="inlineStr">
         <is>
-          <t>docs/evidencias_testes/2026-10-03/03_alertas_api_real.png</t>
+          <t>docs/evidencias_testes/2026-10-03/03_alertas_api_real.png; docs/evidencias_testes/usabilidade/analise_usabilidade_2026-10-29.md; docs/evidencias_testes/usabilidade/respostas_formulario_2026-10.csv</t>
         </is>
       </c>
       <c r="P13" s="8" t="inlineStr">
         <is>
-          <t>João (automação adb no emulador)</t>
+          <t>Grupo (formulário) e João (análise e melhorias)</t>
         </is>
       </c>
       <c r="Q13" s="8" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
-        </is>
-      </c>
-      <c r="R13" s="8" t="inlineStr"/>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>Avaliação sem uso do app pelos participantes (só as telas) e amostra de conveniência (familiares e amigos): ver limitações em T16_secao_metodologia_testes.md.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="36" customHeight="1" s="6">
       <c r="A14" s="8" t="inlineStr">
@@ -2240,34 +2244,34 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Funcional OK: mapa do Google carregado (sem 'Authorization failure' no logcat) com as 30 ocorrências de demonstração da API como marcadores coloridos por nível (cartão 'Situação atual': 9 alto, 8 médio, 13 baixo) e enquadramento em São Caetano do Sul. Posição conferida: marcador da ocorrência nº 879 em -23.6124, -46.5754, igual a GET /ocorrencias/879. Avaliação de usabilidade com participantes externos ainda pendente.</t>
+          <t>Parte funcional aprovada em emulador (ver evidências anteriores). Avaliação de usabilidade por questionário sobre as capturas das telas (Google Forms, 12 participantes que aceitaram o termo, 17 a 21/10/2026): tela Mapa com média 4,73 em 5 (critério ≥ 4). 10 de 12 entenderam cores e marcadores esmaecidos (2 só as cores). Melhoria aplicada em 29/10/2026: Resumo do mapa passou a servir de legenda das cores e a explicar os esmaecidos.</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>Em Execução</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="8" t="inlineStr">
         <is>
-          <t>docs/evidencias_testes/2026-10-07/01_mapa_marcadores.png</t>
+          <t>docs/evidencias_testes/2026-10-07/01_mapa_marcadores.png; docs/evidencias_testes/usabilidade/analise_usabilidade_2026-10-29.md; docs/evidencias_testes/usabilidade/respostas_formulario_2026-10.csv</t>
         </is>
       </c>
       <c r="P15" s="8" t="inlineStr">
         <is>
-          <t>João (automação adb no emulador)</t>
+          <t>Grupo (formulário) e João (análise e melhorias)</t>
         </is>
       </c>
       <c r="Q15" s="8" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>03/10/2026: Bloqueado (chave do Google Maps restrita a outros certificados). Desbloqueado em 07/10/2026 com o cadastro do SHA-1 do certificado de depuração do notebook de testes nas restrições da chave. Execução com as 30 ocorrências; desde 07/10/2026 o mapa mostra só as das últimas 24 h (CT-MAP-003).</t>
+          <t>03/10/2026: Bloqueado (chave do Google Maps restrita a outros certificados). Desbloqueado em 07/10/2026 com o cadastro do SHA-1 do certificado de depuração do notebook de testes nas restrições da chave. Execução com as 30 ocorrências; desde 07/10/2026 o mapa mostra só as das últimas 24 h (CT-MAP-003). Avaliação sem uso do app pelos participantes (só as telas) e amostra de conveniência (familiares e amigos): ver limitações em T16_secao_metodologia_testes.md.</t>
         </is>
       </c>
     </row>
@@ -2325,34 +2329,34 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Funcional OK: toque no marcador abre o painel da ocorrência (descrição, coordenadas, nível, fonte e data/hora) e o botão 'Ver detalhes' abre a tela de detalhes da mesma ocorrência (nº 879, dados iguais aos de GET /ocorrencias/879). Avaliação de usabilidade com participantes externos ainda pendente.</t>
+          <t>Parte funcional aprovada em emulador (ver evidências anteriores). Avaliação de usabilidade por questionário sobre as capturas das telas (Google Forms, 12 participantes que aceitaram o termo, 17 a 21/10/2026): tela Mapa com média 4,73 em 5 (critério ≥ 4). Navegação mapa → detalhes avaliada pelas capturas das duas telas (sem tarefa no app).</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>Em Execução</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="8" t="inlineStr">
         <is>
-          <t>docs/evidencias_testes/2026-10-07/02_mapa_marcador_selecionado.png; docs/evidencias_testes/2026-10-07/03_mapa_para_detalhes.png</t>
+          <t>docs/evidencias_testes/2026-10-07/02_mapa_marcador_selecionado.png; docs/evidencias_testes/2026-10-07/03_mapa_para_detalhes.png; docs/evidencias_testes/usabilidade/analise_usabilidade_2026-10-29.md; docs/evidencias_testes/usabilidade/respostas_formulario_2026-10.csv</t>
         </is>
       </c>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>João (automação adb no emulador)</t>
+          <t>Grupo (formulário) e João (análise e melhorias)</t>
         </is>
       </c>
       <c r="Q16" s="8" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>A navegação tem dois passos (marcador → painel → 'Ver detalhes'), não um: o painel permite conferir a ocorrência antes de sair do mapa. Desbloqueado em 07/10/2026 (ver CT-MAP-001).</t>
+          <t>A navegação tem dois passos (marcador → painel → 'Ver detalhes'), não um: o painel permite conferir a ocorrência antes de sair do mapa. Desbloqueado em 07/10/2026 (ver CT-MAP-001). Avaliação sem uso do app pelos participantes (só as telas) e amostra de conveniência (familiares e amigos): ver limitações em T16_secao_metodologia_testes.md.</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2414,12 @@
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>Funcional OK: GET /ocorrencias/{id} 200; tela exibe nº, descrição, nível, fonte, data/hora e coordenadas. Avaliação de usabilidade com participantes externos ainda pendente.</t>
+          <t>Parte funcional aprovada em emulador (ver evidências anteriores). Avaliação de usabilidade por questionário sobre as capturas das telas (Google Forms, 12 participantes que aceitaram o termo, 17 a 21/10/2026): tela Detalhes com média 4,90 em 5 (critério ≥ 4). 9 de 12 acharam as informações suficientes (3 sentiram falta de endereço/bairro). Melhoria aplicada em 29/10/2026: Endereço aproximado (rua e bairro) incluído.</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>Em Execução</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
@@ -2430,22 +2434,22 @@
       </c>
       <c r="O17" s="8" t="inlineStr">
         <is>
-          <t>docs/evidencias_testes/2026-10-03/05_cadastro_manual_detalhes.png</t>
+          <t>docs/evidencias_testes/2026-10-03/05_cadastro_manual_detalhes.png; docs/evidencias_testes/usabilidade/analise_usabilidade_2026-10-29.md; docs/evidencias_testes/usabilidade/respostas_formulario_2026-10.csv</t>
         </is>
       </c>
       <c r="P17" s="8" t="inlineStr">
         <is>
-          <t>João (automação adb no emulador)</t>
+          <t>Grupo (formulário) e João (análise e melhorias)</t>
         </is>
       </c>
       <c r="Q17" s="8" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>BUG-002: com o aparelho em português, as coordenadas saíam '-23,6148, -46,5435' (vírgula decimal confundida com a separadora). Corrigido em 03/10/2026 (sempre ponto decimal) e reverificado em pt-BR.</t>
+          <t>BUG-002: com o aparelho em português, as coordenadas saíam '-23,6148, -46,5435' (vírgula decimal confundida com a separadora). Corrigido em 03/10/2026 (sempre ponto decimal) e reverificado em pt-BR. Avaliação sem uso do app pelos participantes (só as telas) e amostra de conveniência (familiares e amigos): ver limitações em T16_secao_metodologia_testes.md.</t>
         </is>
       </c>
     </row>
@@ -2589,34 +2593,34 @@
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>Funcional OK: bairro salvo no perfil e mantido depois de fechar e reabrir o app (cartão em Ajustes: 'Olímpico • São Caetano do Sul'). Avaliação de usabilidade com participantes externos ainda pendente.</t>
+          <t>Parte funcional aprovada em emulador (ver evidências anteriores). Avaliação de usabilidade por questionário sobre as capturas das telas (Google Forms, 12 participantes que aceitaram o termo, 17 a 21/10/2026): tela Ajustes com média 4,83 em 5 (critério ≥ 4). 11 de 12 acharam as opções claras (1 em parte).</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>Em Execução</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="8" t="inlineStr">
         <is>
-          <t>docs/evidencias_testes/2026-10-03/07_perfil_persistido.png</t>
+          <t>docs/evidencias_testes/2026-10-03/07_perfil_persistido.png; docs/evidencias_testes/usabilidade/analise_usabilidade_2026-10-29.md; docs/evidencias_testes/usabilidade/respostas_formulario_2026-10.csv</t>
         </is>
       </c>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>João (automação adb no emulador)</t>
+          <t>Grupo (formulário) e João (análise e melhorias)</t>
         </is>
       </c>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>Perfil e preferências ficam só no aparelho (SharedPreferences) — o backend não tem tabela de usuários.</t>
+          <t>Perfil e preferências ficam só no aparelho (SharedPreferences) — o backend não tem tabela de usuários. Avaliação sem uso do app pelos participantes (só as telas) e amostra de conveniência (familiares e amigos): ver limitações em T16_secao_metodologia_testes.md.</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2642,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Acessar a tela de login e avançar para a área principal</t>
+          <t>Acessar a tela de entrada (sem cadastro nem senha desde 29/10/2026) e avançar para a área principal</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -2675,34 +2679,34 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Funcional OK: nome e senha quaisquer levam à área principal; sessão mantida ao reabrir o app. Avaliação de usabilidade com participantes externos ainda pendente.</t>
+          <t>Parte funcional aprovada em emulador (ver evidências anteriores). Avaliação de usabilidade por questionário sobre as capturas das telas (Google Forms, 12 participantes que aceitaram o termo, 17 a 21/10/2026): tela Entrada com média 4,90 em 5 (critério ≥ 4). 10 de 12 acharam claro o aviso de senha (2 mais ou menos). Melhoria aplicada em 29/10/2026: Campo de senha retirado: entrada sem cadastro nem senha, nome opcional.</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>Em Execução</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="8" t="inlineStr"/>
       <c r="O20" s="8" t="inlineStr">
         <is>
-          <t>docs/evidencias_testes/2026-10-03/01_login.png</t>
+          <t>docs/evidencias_testes/2026-10-03/01_login.png; docs/evidencias_testes/usabilidade/analise_usabilidade_2026-10-29.md; docs/evidencias_testes/usabilidade/respostas_formulario_2026-10.csv</t>
         </is>
       </c>
       <c r="P20" s="8" t="inlineStr">
         <is>
-          <t>João (automação adb no emulador)</t>
+          <t>Grupo (formulário) e João (análise e melhorias)</t>
         </is>
       </c>
       <c r="Q20" s="8" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>Login não implementa autenticação real; não faz parte do escopo do sistema.</t>
+          <t>Login não implementa autenticação real; não faz parte do escopo do sistema. Avaliação sem uso do app pelos participantes (só as telas) e amostra de conveniência (familiares e amigos): ver limitações em T16_secao_metodologia_testes.md.</t>
         </is>
       </c>
     </row>
@@ -3617,34 +3621,34 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>Funcional OK: os 5 cartões de fonte e o cartão 'Como o risco é calculado' abrem com o texto previsto; rótulos sem a fonte entre parênteses. Avaliação com participantes externos pendente.</t>
+          <t>Parte funcional aprovada em emulador (ver evidências anteriores). Avaliação de usabilidade por questionário sobre as capturas das telas (Google Forms, 12 participantes que aceitaram o termo, 17 a 21/10/2026): tela Previsão com média 4,77 em 5 (critério ≥ 4). 11 de 12 entenderam o risco Baixo com aviso do INMET (1 em dúvida).</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>Em Execução</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n"/>
       <c r="O31" s="8" t="inlineStr">
         <is>
-          <t>docs/evidencias_testes/2026-10-07/07_previsao_info_fonte_ana.png; docs/evidencias_testes/2026-10-07/08_previsao_info_risco.png</t>
+          <t>docs/evidencias_testes/2026-10-07/07_previsao_info_fonte_ana.png; docs/evidencias_testes/2026-10-07/08_previsao_info_risco.png; docs/evidencias_testes/usabilidade/analise_usabilidade_2026-10-29.md; docs/evidencias_testes/usabilidade/respostas_formulario_2026-10.csv</t>
         </is>
       </c>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>João (automação adb no emulador)</t>
+          <t>Grupo (formulário) e João (análise e melhorias)</t>
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>Pedido do João em 07/10/2026: a origem dos dados e a explicação do cálculo saíram do texto da tela e foram para ícones ⓘ (área de toque de 48 dp, com descrição para leitor de tela).</t>
+          <t>Pedido do João em 07/10/2026: a origem dos dados e a explicação do cálculo saíram do texto da tela e foram para ícones ⓘ (área de toque de 48 dp, com descrição para leitor de tela). Avaliação sem uso do app pelos participantes (só as telas) e amostra de conveniência (familiares e amigos): ver limitações em T16_secao_metodologia_testes.md.</t>
         </is>
       </c>
     </row>
